--- a/data/stx_xlsx/EPROb.ST.xlsx
+++ b/data/stx_xlsx/EPROb.ST.xlsx
@@ -8662,12 +8662,8 @@
       <c r="A108" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="16">
-        <v>594.85</v>
-      </c>
-      <c r="C108" s="16">
-        <v>157.3</v>
-      </c>
+      <c r="B108" s="16"/>
+      <c r="C108" s="16"/>
       <c r="D108" s="15"/>
       <c r="E108" s="15"/>
       <c r="F108" s="15"/>
